--- a/artfynd/A 12887-2026 artfynd.xlsx
+++ b/artfynd/A 12887-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126053130</v>
+        <v>126053153</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126053153</v>
+        <v>126053041</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -818,7 +818,11 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -831,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372708</v>
+        <v>372878</v>
       </c>
       <c r="R3" t="n">
-        <v>6626887</v>
+        <v>6627004</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt i blåbärsriset</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +899,115 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126053130</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långvattnet SV, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>372708</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626887</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
